--- a/artfynd/A 17731-2019 artfynd.xlsx
+++ b/artfynd/A 17731-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 17731-2019 artfynd.xlsx
+++ b/artfynd/A 17731-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4264,132 +4264,6 @@
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>86555951</v>
-      </c>
-      <c r="B32" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Senneby, Ö om (*knärot* /stjälk/), Upl</t>
-        </is>
-      </c>
-      <c r="Q32" t="n">
-        <v>717141.8865628212</v>
-      </c>
-      <c r="R32" t="n">
-        <v>6653755.697423554</v>
-      </c>
-      <c r="S32" t="n">
-        <v>5</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Stockholm</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Norrtälje</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>Väddö</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>AB-Nor-1731</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>2016-09-01</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>2016-09-01</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Obs: Flera dellokaler. Se privata obsar! Senneby, Ö om, Obskoord: 6653414/1672296/5 m (). Gammal barrblandskog på kalkrik mark.</t>
-        </is>
-      </c>
-      <c r="AD32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="inlineStr"/>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>Jan Yngve Andersson</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>Kjell  Andersson, Bo Törnquist</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
